--- a/hpi_scraper/JobsHiring/theirstack/theirstack_api_report.xlsx
+++ b/hpi_scraper/JobsHiring/theirstack/theirstack_api_report.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>ratelimit: "per-second";r=3;t=1;pk=757365723a6c6c616b613239333740676d61696c2e636f6d, "per-minute";r=9;t=7;pk=757365723a6c6c616b613239333740676d61696c2e636f6d, "per-hour";r=49;t=2647;pk=757365723a6c6c616b613239333740676d61696c2e636f6d, "per-day";r=399;t=42247;pk=757365723a6c6c616b613239333740676d61696c2e636f6d; ratelimit-limit: 4, 10, 50, 400; ratelimit-policy: "per-second";q=4;w=1, "per-minute";q=10;w=60, "per-hour";q=50;w=3600, "per-day";q=400;w=86400; ratelimit-remaining: 3, 9, 49, 399; ratelimit-reset: 1, 7, 2647, 42247</t>
+          <t>ratelimit: "per-second";r=3;t=1;pk=757365723a6c6c616b613239333740676d61696c2e636f6d, "per-minute";r=9;t=45;pk=757365723a6c6c616b613239333740676d61696c2e636f6d, "per-hour";r=45;t=525;pk=757365723a6c6c616b613239333740676d61696c2e636f6d, "per-day";r=395;t=40125;pk=757365723a6c6c616b613239333740676d61696c2e636f6d; ratelimit-limit: 4, 10, 50, 400; ratelimit-policy: "per-second";q=4;w=1, "per-minute";q=10;w=60, "per-hour";q=50;w=3600, "per-day";q=400;w=86400; ratelimit-remaining: 3, 9, 45, 395; ratelimit-reset: 1, 45, 525, 40125</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>5.862 avg</t>
+          <t>5.883 avg</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">

--- a/hpi_scraper/JobsHiring/theirstack/theirstack_api_report.xlsx
+++ b/hpi_scraper/JobsHiring/theirstack/theirstack_api_report.xlsx
@@ -449,15 +449,15 @@
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="72" customWidth="1" min="5" max="5"/>
+    <col width="72" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="19" customWidth="1" min="12" max="12"/>
-    <col width="70" customWidth="1" min="13" max="13"/>
+    <col width="32" customWidth="1" min="11" max="11"/>
+    <col width="66" customWidth="1" min="12" max="12"/>
+    <col width="72" customWidth="1" min="13" max="13"/>
     <col width="24" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -556,23 +556,19 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>12 API credits used in this run; TheirStack job search consumes 1 credit per returned job</t>
+          <t>12 TheirStack job-search credits used; one credit per returned job record.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>ratelimit: "per-second";r=3;t=1;pk=757365723a6c6c616b613239333740676d61696c2e636f6d, "per-minute";r=9;t=45;pk=757365723a6c6c616b613239333740676d61696c2e636f6d, "per-hour";r=45;t=525;pk=757365723a6c6c616b613239333740676d61696c2e636f6d, "per-day";r=395;t=40125;pk=757365723a6c6c616b613239333740676d61696c2e636f6d; ratelimit-limit: 4, 10, 50, 400; ratelimit-policy: "per-second";q=4;w=1, "per-minute";q=10;w=60, "per-hour";q=50;w=3600, "per-day";q=400;w=86400; ratelimit-remaining: 3, 9, 45, 395; ratelimit-reset: 1, 45, 525, 40125</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+          <t>TheirStack returned per-second, per-minute, per-hour and per-day quota headers; request completed within limits.</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
@@ -586,17 +582,17 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>12 sampled active job records.</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>No - sampled jobs, role mix and location signals were available.</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>TheirStack gives total counts via metadata and sampled active job details from job search.</t>
+          <t>Good secondary hiring source. Use it to validate active job themes against Coresignal rather than as the only total-count source.</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
